--- a/result.xlsx
+++ b/result.xlsx
@@ -134,7 +134,7 @@
     <t>22.68</t>
   </si>
   <si>
-    <t>爬虫未返回数据</t>
+    <t>Node爬虫微服务宕机</t>
   </si>
   <si>
     <t>Толкушка для картофеля, 30 см</t>
